--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92224</v>
+        <v>92225</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92792</v>
+        <v>92793</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92225</v>
+        <v>92252</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92793</v>
+        <v>92820</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92252</v>
+        <v>92257</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92820</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92257</v>
+        <v>92262</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92262</v>
+        <v>92266</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92836</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92266</v>
+        <v>92271</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92836</v>
+        <v>92841</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92279</v>
+        <v>92284</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92849</v>
+        <v>92854</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92284</v>
+        <v>92287</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92854</v>
+        <v>92857</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92287</v>
+        <v>92294</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92857</v>
+        <v>92864</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92294</v>
+        <v>92301</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92864</v>
+        <v>92871</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 28215-2022 artfynd.xlsx
+++ b/artfynd/A 28215-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128757213</v>
       </c>
       <c r="B2" t="n">
-        <v>92301</v>
+        <v>92303</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -787,7 +787,7 @@
         <v>128757324</v>
       </c>
       <c r="B3" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -888,7 +888,7 @@
         <v>128757271</v>
       </c>
       <c r="B4" t="n">
-        <v>92871</v>
+        <v>92873</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
